--- a/data/BlindVision__dataset (1).xlsx
+++ b/data/BlindVision__dataset (1).xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -474,7 +474,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>842 annotated test objects, fully accounted for in the ten-class confusion matrix (Confusion_Matrix.csv / Table IV); the Classwise_Evaluation sheet's per-class TP/FP/FN are recomputed from that matrix (diagonal, column excess, row excess respectively) so the two sheets agree.</t>
+          <t>842 annotated test objects in the ten-class confusion matrix (Confusion_Matrix.csv / Table IV). The Classwise_Evaluation sheet is recomputed from that matrix; per-class AP values are not included.</t>
         </is>
       </c>
     </row>
@@ -535,6 +535,18 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>Where the supplied specification contains aggregate values without raw observations, this workbook does not falsely claim those missing raw observations are original measurements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>YOLO_Metrics sheet</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Six-point summary (every 10 epochs) of the original training run supplied by the authors; not a raw Ultralytics export. The raw per-epoch log is not included.</t>
         </is>
       </c>
     </row>
@@ -1036,11 +1048,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.963</v>
+        <v>0.922</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>92.2%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1114,44 +1126,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Detected Samples</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Error 1</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Error 2</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Precision</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ground-truth instances</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Correct (diagonal)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Predicted as this class in error (column off-diagonal)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Missed as another class (row off-diagonal)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Precision (inter-class only; excludes 31 unmatched background FPs)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Recall</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>mAP@0.5</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>mAP@0.5:0.95</t>
         </is>
       </c>
     </row>
@@ -1162,25 +1169,22 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>115</v>
+      </c>
+      <c r="C2" t="n">
         <v>110</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.973</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.957</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.991</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.861</v>
       </c>
     </row>
     <row r="3">
@@ -1190,25 +1194,22 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3" t="n">
         <v>75</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.974</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.962</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.824</v>
       </c>
     </row>
     <row r="4">
@@ -1218,25 +1219,22 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>92</v>
+      </c>
+      <c r="C4" t="n">
         <v>88</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.967</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.957</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.801</v>
       </c>
     </row>
     <row r="5">
@@ -1246,25 +1244,22 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>65</v>
+      </c>
+      <c r="C5" t="n">
         <v>61</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.953</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.9379999999999999</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.8159999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1274,25 +1269,22 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>55</v>
+      </c>
+      <c r="C6" t="n">
         <v>53</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.981</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.964</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.969</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.793</v>
       </c>
     </row>
     <row r="7">
@@ -1302,25 +1294,22 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" t="n">
         <v>66</v>
-      </c>
-      <c r="C7" t="n">
-        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9429999999999999</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>0.9429999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.781</v>
+        <v>0.9429999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1330,25 +1319,22 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>124</v>
+      </c>
+      <c r="C8" t="n">
         <v>120</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>4</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.984</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>0.968</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.805</v>
       </c>
     </row>
     <row r="9">
@@ -1358,25 +1344,22 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>88</v>
+      </c>
+      <c r="C9" t="n">
         <v>84</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>3</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>4</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.966</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.955</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.847</v>
       </c>
     </row>
     <row r="10">
@@ -1386,25 +1369,22 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>60</v>
+      </c>
+      <c r="C10" t="n">
         <v>57</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0.95</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>0.95</v>
       </c>
       <c r="G10" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.829</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="11">
@@ -1414,25 +1394,47 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>95</v>
+      </c>
+      <c r="C11" t="n">
         <v>91</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>13</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.875</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.958</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.977</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.8120000000000001</v>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>842</v>
+      </c>
+      <c r="C12" t="n">
+        <v>805</v>
+      </c>
+      <c r="D12" t="n">
+        <v>37</v>
+      </c>
+      <c r="E12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.956</v>
       </c>
     </row>
   </sheetData>
@@ -1599,7 +1601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1608,17 +1610,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Calculation</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1632,7 +1634,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10 class IDs: 0–9</t>
+          <t>10 class IDs: 0-9 (data/Class_Definition.csv)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1644,12 +1646,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power mean current</t>
+          <t>Confusion matrix total</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(2.38+2.41+2.39+2.42+2.40)/5 = 2.400 A</t>
+          <t>Sum of all cells in data/Confusion_Matrix.csv = 842 ground-truth instances</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1661,12 +1663,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power mean</t>
+          <t>Confusion matrix diagonal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(12.04+12.15+12.07+12.17+12.10)/5 = 12.106 W</t>
+          <t>Sum of diagonal = 805 correct classifications; off-diagonal = 37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1678,12 +1680,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mean V × mean I</t>
+          <t>Pooled precision (Table II)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.044 × 2.400 = 12.106 W</t>
+          <t>805 / (805 + 37 inter-class + 31 unmatched background FP) = 805/873 = 0.922</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1695,12 +1697,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Battery mean current</t>
+          <t>Recall (Table II)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mean of 11 values = 1.472 A</t>
+          <t>805 / 842 = 0.956</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1712,12 +1714,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Validation/test separation</t>
+          <t>F1 (Table II)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.98/0.96/0.99/0.85 vs 0.963/0.956/0.968/0.765</t>
+          <t>2 x 0.922 x 0.956 / (0.922 + 0.956) = 0.939</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1729,15 +1731,100 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Latency arithmetic</t>
+          <t>False positives per image (Table III)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10 trial means average to 121.875 ms</t>
+          <t>31 / 700 = 0.044</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Classwise vs confusion matrix</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>data/Classwise_Evaluation.csv per-class counts recomputed from data/Confusion_Matrix.csv</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Power mean current</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(2.38+2.41+2.39+2.42+2.40)/5 = 2.400 A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Power mean</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(12.04+12.15+12.07+12.17+12.10)/5 = 12.106 W</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mean V x mean I</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5.044 x 2.400 = 12.106 W</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Navigation outcomes</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>data/raw/participant_trial_outcomes_100.csv: 96 of 100 outcomes = 1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
